--- a/Luban/Excel/角色战斗属性.xlsx
+++ b/Luban/Excel/角色战斗属性.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A2BA8F-F97E-4921-AF72-6C3E68832D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,17 +35,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>think</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="10"/>
             <rFont val="微软雅黑"/>
+            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t>1 - 人
@@ -413,14 +420,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,6 +433,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -439,353 +441,32 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -808,255 +489,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1066,98 +505,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1442,26 +828,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD88"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="10.2222222222222" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="2"/>
     <col min="6" max="25" width="9" style="1"/>
-    <col min="26" max="26" width="8.88888888888889" style="1" customWidth="1"/>
+    <col min="26" max="26" width="8.875" style="1" customWidth="1"/>
     <col min="27" max="27" width="9" style="1"/>
-    <col min="28" max="28" width="11.2222222222222" style="1" customWidth="1"/>
+    <col min="28" max="28" width="11.25" style="1" customWidth="1"/>
     <col min="29" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:30">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1478,157 +864,157 @@
       <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="11" t="s">
+      <c r="R1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AA1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AB1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AD1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" ht="15.6" spans="1:30">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="V2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="X2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-    </row>
-    <row r="3" ht="15.6" spans="1:30">
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>51</v>
       </c>
@@ -1637,81 +1023,81 @@
         <v>52</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="10"/>
+      <c r="G3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="P3" s="11" t="s">
+      <c r="P3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="11" t="s">
+      <c r="Q3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="R3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="S3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="T3" s="11" t="s">
+      <c r="T3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="11" t="s">
+      <c r="U3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="V3" s="11" t="s">
+      <c r="V3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="W3" s="11" t="s">
+      <c r="W3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="X3" s="11" t="s">
+      <c r="X3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="Y3" s="11" t="s">
+      <c r="Y3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="Z3" s="11" t="s">
+      <c r="Z3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="AA3" s="11" t="s">
+      <c r="AA3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="AB3" s="11"/>
-      <c r="AC3" s="11"/>
-      <c r="AD3" s="11" t="s">
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="12">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A4" s="11">
         <v>800001</v>
       </c>
       <c r="E4" s="2">
@@ -1766,7 +1152,7 @@
         <v>35</v>
       </c>
       <c r="V4" s="1">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="W4" s="1">
         <v>10</v>
@@ -1781,8 +1167,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="12">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A5" s="11">
         <v>800002</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1855,8 +1241,8 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="12">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A6" s="11">
         <v>800003</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -1929,8 +1315,8 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="12">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A7" s="11">
         <v>800004</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2003,8 +1389,8 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
-      <c r="A8" s="12">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A8" s="11">
         <v>800005</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -2077,8 +1463,8 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
-      <c r="A9" s="12">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A9" s="11">
         <v>800006</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2151,11 +1537,11 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
-      <c r="A10" s="12">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A10" s="11">
         <v>800007</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>55</v>
       </c>
       <c r="E10" s="2">
@@ -2225,22 +1611,22 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="12">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A11" s="11">
         <v>800008</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>56</v>
       </c>
       <c r="E11" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
-      <c r="A12" s="12">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A12" s="11">
         <v>800009</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E12" s="2">
@@ -2295,7 +1681,7 @@
         <v>33</v>
       </c>
       <c r="V12" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="W12" s="1">
         <v>10</v>
@@ -2310,11 +1696,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="12">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A13" s="11">
         <v>800010</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E13" s="2">
@@ -2363,13 +1749,13 @@
         <v>36</v>
       </c>
       <c r="T13" s="1">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="U13" s="1">
         <v>34</v>
       </c>
       <c r="V13" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="W13" s="1">
         <v>10</v>
@@ -2384,11 +1770,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
-      <c r="A14" s="12">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A14" s="11">
         <v>800011</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>57</v>
       </c>
       <c r="E14" s="2">
@@ -2407,7 +1793,7 @@
         <v>174</v>
       </c>
       <c r="J14" s="1">
-        <v>17.4</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="K14" s="1">
         <v>68</v>
@@ -2419,7 +1805,7 @@
         <v>82</v>
       </c>
       <c r="N14" s="1">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="O14" s="1">
         <v>1400</v>
@@ -2458,11 +1844,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
-      <c r="A15" s="12">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A15" s="11">
         <v>800012</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="2">
@@ -2478,11 +1864,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
-      <c r="A16" s="12">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A16" s="11">
         <v>800013</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>59</v>
       </c>
       <c r="E16" s="2">
@@ -2498,11 +1884,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:26">
-      <c r="A17" s="12">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A17" s="11">
         <v>800014</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>59</v>
       </c>
       <c r="E17" s="2">
@@ -2518,11 +1904,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:26">
-      <c r="A18" s="12">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A18" s="11">
         <v>800015</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>61</v>
       </c>
       <c r="E18" s="2">
@@ -2592,11 +1978,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:26">
-      <c r="A19" s="12">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A19" s="11">
         <v>800016</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>61</v>
       </c>
       <c r="E19" s="2">
@@ -2666,11 +2052,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:26">
-      <c r="A20" s="12">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A20" s="11">
         <v>800017</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="11" t="s">
         <v>61</v>
       </c>
       <c r="E20" s="2">
@@ -2719,7 +2105,7 @@
         <v>34</v>
       </c>
       <c r="T20" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="U20" s="1">
         <v>32</v>
@@ -2740,11 +2126,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:26">
-      <c r="A21" s="12">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A21" s="11">
         <v>800018</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="11" t="s">
         <v>63</v>
       </c>
       <c r="E21" s="2">
@@ -2793,7 +2179,7 @@
         <v>34</v>
       </c>
       <c r="T21" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="U21" s="1">
         <v>32</v>
@@ -2814,11 +2200,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:26">
-      <c r="A22" s="12">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A22" s="11">
         <v>800019</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="11" t="s">
         <v>63</v>
       </c>
       <c r="E22" s="2">
@@ -2837,7 +2223,7 @@
         <v>174</v>
       </c>
       <c r="J22" s="1">
-        <v>17.4</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="K22" s="1">
         <v>63</v>
@@ -2861,13 +2247,13 @@
         <v>132</v>
       </c>
       <c r="R22" s="1">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="S22" s="1">
         <v>36</v>
       </c>
       <c r="T22" s="1">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="U22" s="1">
         <v>33</v>
@@ -2888,11 +2274,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:26">
-      <c r="A23" s="12">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A23" s="11">
         <v>800020</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="11" t="s">
         <v>63</v>
       </c>
       <c r="E23" s="2">
@@ -2962,11 +2348,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:26">
-      <c r="A24" s="12">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A24" s="11">
         <v>800021</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="11" t="s">
         <v>65</v>
       </c>
       <c r="E24" s="2">
@@ -3015,13 +2401,13 @@
         <v>35</v>
       </c>
       <c r="T24" s="1">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="U24" s="1">
         <v>34</v>
       </c>
       <c r="V24" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="W24" s="1">
         <v>10</v>
@@ -3036,11 +2422,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:26">
-      <c r="A25" s="12">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A25" s="11">
         <v>800022</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="11" t="s">
         <v>66</v>
       </c>
       <c r="E25" s="2">
@@ -3049,28 +2435,28 @@
       <c r="F25" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="1">
         <v>220</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="1">
         <v>22</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="1">
         <v>185</v>
       </c>
-      <c r="J25" s="13">
+      <c r="J25" s="1">
         <v>18.5</v>
       </c>
-      <c r="K25" s="13">
+      <c r="K25" s="1">
         <v>68</v>
       </c>
-      <c r="L25" s="13">
+      <c r="L25" s="1">
         <v>6.8</v>
       </c>
-      <c r="M25" s="13">
+      <c r="M25" s="1">
         <v>56</v>
       </c>
-      <c r="N25" s="13">
+      <c r="N25" s="1">
         <v>5.6</v>
       </c>
       <c r="O25" s="1">
@@ -3089,13 +2475,13 @@
         <v>35</v>
       </c>
       <c r="T25" s="1">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="U25" s="1">
         <v>33</v>
       </c>
       <c r="V25" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="W25" s="1">
         <v>10</v>
@@ -3110,11 +2496,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:26">
-      <c r="A26" s="12">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A26" s="11">
         <v>800023</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="11" t="s">
         <v>66</v>
       </c>
       <c r="E26" s="2">
@@ -3123,28 +2509,28 @@
       <c r="F26" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="1">
         <v>216</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="1">
         <v>21.6</v>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="1">
         <v>166</v>
       </c>
-      <c r="J26" s="13">
-        <v>16.6</v>
-      </c>
-      <c r="K26" s="13">
+      <c r="J26" s="1">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="K26" s="1">
         <v>74</v>
       </c>
-      <c r="L26" s="13">
+      <c r="L26" s="1">
         <v>7.4</v>
       </c>
-      <c r="M26" s="13">
+      <c r="M26" s="1">
         <v>67</v>
       </c>
-      <c r="N26" s="13">
+      <c r="N26" s="1">
         <v>6.7</v>
       </c>
       <c r="O26" s="1">
@@ -3157,19 +2543,19 @@
         <v>125</v>
       </c>
       <c r="R26" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="S26" s="1">
         <v>34</v>
       </c>
       <c r="T26" s="1">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="U26" s="1">
         <v>33</v>
       </c>
       <c r="V26" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="W26" s="1">
         <v>10</v>
@@ -3184,11 +2570,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:26">
-      <c r="A27" s="12">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A27" s="11">
         <v>800024</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="11" t="s">
         <v>66</v>
       </c>
       <c r="E27" s="2">
@@ -3197,28 +2583,28 @@
       <c r="F27" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="1">
         <v>204</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="1">
         <v>2.04</v>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="1">
         <v>177</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="1">
         <v>17.7</v>
       </c>
-      <c r="K27" s="13">
+      <c r="K27" s="1">
         <v>70</v>
       </c>
-      <c r="L27" s="13">
+      <c r="L27" s="1">
         <v>7</v>
       </c>
-      <c r="M27" s="13">
+      <c r="M27" s="1">
         <v>77</v>
       </c>
-      <c r="N27" s="13">
+      <c r="N27" s="1">
         <v>7.7</v>
       </c>
       <c r="O27" s="1">
@@ -3231,13 +2617,13 @@
         <v>122</v>
       </c>
       <c r="R27" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="S27" s="1">
         <v>33</v>
       </c>
       <c r="T27" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="U27" s="1">
         <v>32</v>
@@ -3258,11 +2644,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:26">
-      <c r="A28" s="12">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A28" s="11">
         <v>800025</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="11" t="s">
         <v>67</v>
       </c>
       <c r="E28" s="2">
@@ -3332,11 +2718,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:26">
-      <c r="A29" s="12">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A29" s="11">
         <v>800026</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="11" t="s">
         <v>67</v>
       </c>
       <c r="E29" s="2">
@@ -3379,7 +2765,7 @@
         <v>124</v>
       </c>
       <c r="R29" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="S29" s="1">
         <v>36</v>
@@ -3406,11 +2792,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:26">
-      <c r="A30" s="12">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A30" s="11">
         <v>800027</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="11" t="s">
         <v>67</v>
       </c>
       <c r="E30" s="2">
@@ -3441,7 +2827,7 @@
         <v>82</v>
       </c>
       <c r="N30" s="1">
-        <v>8.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="O30" s="1">
         <v>1280</v>
@@ -3453,7 +2839,7 @@
         <v>132</v>
       </c>
       <c r="R30" s="1">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="S30" s="1">
         <v>34</v>
@@ -3480,8 +2866,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:26">
-      <c r="A31" s="12">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A31" s="11">
         <v>800028</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -3551,8 +2937,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:26">
-      <c r="A32" s="12">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A32" s="11">
         <v>800029</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -3604,13 +2990,13 @@
         <v>35</v>
       </c>
       <c r="T32" s="1">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="U32" s="1">
         <v>33</v>
       </c>
       <c r="V32" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="W32" s="1">
         <v>10</v>
@@ -3625,8 +3011,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:26">
-      <c r="A33" s="12">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A33" s="11">
         <v>800030</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -3699,8 +3085,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:26">
-      <c r="A34" s="12">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A34" s="11">
         <v>800031</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -3752,7 +3138,7 @@
         <v>33</v>
       </c>
       <c r="T34" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="U34" s="1">
         <v>30</v>
@@ -3773,8 +3159,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:26">
-      <c r="A35" s="12">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A35" s="11">
         <v>800032</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -3826,13 +3212,13 @@
         <v>36</v>
       </c>
       <c r="T35" s="1">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="U35" s="1">
         <v>33</v>
       </c>
       <c r="V35" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="W35" s="1">
         <v>10</v>
@@ -3847,8 +3233,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:26">
-      <c r="A36" s="12">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A36" s="11">
         <v>800033</v>
       </c>
       <c r="D36" s="1" t="s">
@@ -3900,7 +3286,7 @@
         <v>33</v>
       </c>
       <c r="T36" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="U36" s="1">
         <v>32</v>
@@ -3921,8 +3307,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:26">
-      <c r="A37" s="12">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A37" s="11">
         <v>800034</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -3995,8 +3381,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:26">
-      <c r="A38" s="12">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A38" s="11">
         <v>800035</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -4069,8 +3455,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:26">
-      <c r="A39" s="12">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A39" s="11">
         <v>800036</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -4143,8 +3529,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:26">
-      <c r="A40" s="12">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A40" s="11">
         <v>800037</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -4217,8 +3603,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:26">
-      <c r="A41" s="12">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A41" s="11">
         <v>800038</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -4291,8 +3677,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:26">
-      <c r="A42" s="12">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A42" s="11">
         <v>800039</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -4365,8 +3751,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:26">
-      <c r="A43" s="12">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A43" s="11">
         <v>800040</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -4439,8 +3825,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:26">
-      <c r="A44" s="12">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A44" s="11">
         <v>800041</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -4513,8 +3899,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:26">
-      <c r="A45" s="12">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A45" s="11">
         <v>800042</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -4587,8 +3973,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:26">
-      <c r="A46" s="12">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A46" s="11">
         <v>800043</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -4661,8 +4047,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:26">
-      <c r="A47" s="12">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A47" s="11">
         <v>800044</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -4735,8 +4121,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:26">
-      <c r="A48" s="12">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A48" s="11">
         <v>800045</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -4809,11 +4195,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:26">
-      <c r="A49" s="12">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A49" s="11">
         <v>800046</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="11" t="s">
         <v>77</v>
       </c>
       <c r="E49" s="2">
@@ -4862,7 +4248,7 @@
         <v>35</v>
       </c>
       <c r="T49" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="U49" s="1">
         <v>32</v>
@@ -4883,11 +4269,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:26">
-      <c r="A50" s="12">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A50" s="11">
         <v>800047</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="11" t="s">
         <v>77</v>
       </c>
       <c r="E50" s="2">
@@ -4957,11 +4343,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:26">
-      <c r="A51" s="12">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A51" s="11">
         <v>800048</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="11" t="s">
         <v>77</v>
       </c>
       <c r="E51" s="2">
@@ -5010,13 +4396,13 @@
         <v>36</v>
       </c>
       <c r="T51" s="1">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="U51" s="1">
         <v>34</v>
       </c>
       <c r="V51" s="1">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="W51" s="1">
         <v>10</v>
@@ -5031,11 +4417,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="1:26">
-      <c r="A52" s="12">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A52" s="11">
         <v>800049</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="11" t="s">
         <v>78</v>
       </c>
       <c r="E52" s="2">
@@ -5051,11 +4437,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:26">
-      <c r="A53" s="12">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A53" s="11">
         <v>800050</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="11" t="s">
         <v>78</v>
       </c>
       <c r="E53" s="2">
@@ -5071,11 +4457,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:26">
-      <c r="A54" s="12">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A54" s="11">
         <v>800051</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="11" t="s">
         <v>78</v>
       </c>
       <c r="E54" s="2">
@@ -5091,11 +4477,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:26">
-      <c r="A55" s="12">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A55" s="11">
         <v>800052</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="11" t="s">
         <v>78</v>
       </c>
       <c r="E55" s="2">
@@ -5111,8 +4497,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:26">
-      <c r="A56" s="12">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A56" s="11">
         <v>800053</v>
       </c>
       <c r="D56" s="1" t="s">
@@ -5128,8 +4514,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="1:26">
-      <c r="A57" s="12">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A57" s="11">
         <v>800054</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -5145,8 +4531,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:26">
-      <c r="A58" s="12">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A58" s="11">
         <v>800055</v>
       </c>
       <c r="D58" s="1" t="s">
@@ -5162,66 +4548,66 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="12">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A59" s="11">
         <v>800056</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="11" t="s">
         <v>80</v>
       </c>
       <c r="E59" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="12">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A60" s="11">
         <v>800057</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="11" t="s">
         <v>80</v>
       </c>
       <c r="E60" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="12">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A61" s="11">
         <v>800058</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="11" t="s">
         <v>80</v>
       </c>
       <c r="E61" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="12">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A62" s="11">
         <v>800059</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="11" t="s">
         <v>80</v>
       </c>
       <c r="E62" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="12">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A63" s="11">
         <v>800060</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="11" t="s">
         <v>80</v>
       </c>
       <c r="E63" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:26">
-      <c r="A64" s="12">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A64" s="11">
         <v>800061</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="11" t="s">
         <v>81</v>
       </c>
       <c r="F64" s="1" t="s">
@@ -5234,11 +4620,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="1:26">
-      <c r="A65" s="12">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A65" s="11">
         <v>800062</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="11" t="s">
         <v>82</v>
       </c>
       <c r="Y65" s="1">
@@ -5248,11 +4634,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:26">
-      <c r="A66" s="12">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A66" s="11">
         <v>800063</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="11" t="s">
         <v>83</v>
       </c>
       <c r="Y66" s="1">
@@ -5262,11 +4648,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:26">
-      <c r="A67" s="12">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A67" s="11">
         <v>800064</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="11" t="s">
         <v>84</v>
       </c>
       <c r="Y67" s="1">
@@ -5276,11 +4662,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:26">
-      <c r="A68" s="12">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A68" s="11">
         <v>800065</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="11" t="s">
         <v>85</v>
       </c>
       <c r="F68" s="1" t="s">
@@ -5293,11 +4679,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="1:26">
-      <c r="A69" s="12">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A69" s="11">
         <v>800066</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="11" t="s">
         <v>86</v>
       </c>
       <c r="F69" s="1" t="s">
@@ -5310,11 +4696,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:26">
-      <c r="A70" s="12">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A70" s="11">
         <v>800067</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="D70" s="11" t="s">
         <v>87</v>
       </c>
       <c r="F70" s="1" t="s">
@@ -5327,8 +4713,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:26">
-      <c r="A71" s="12">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A71" s="11">
         <v>800068</v>
       </c>
       <c r="D71" s="1" t="s">
@@ -5344,8 +4730,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:26">
-      <c r="A72" s="12">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A72" s="11">
         <v>800069</v>
       </c>
       <c r="D72" s="1" t="s">
@@ -5361,8 +4747,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:26">
-      <c r="A73" s="12">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A73" s="11">
         <v>800070</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -5378,40 +4764,40 @@
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="12">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A74" s="11">
         <v>800071</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="12">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A75" s="11">
         <v>800072</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="12">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A76" s="11">
         <v>800073</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="12">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A77" s="11">
         <v>800074</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="78" spans="1:26">
-      <c r="A78" s="12">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A78" s="11">
         <v>800075</v>
       </c>
       <c r="D78" s="1" t="s">
@@ -5445,8 +4831,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:26">
-      <c r="A79" s="12">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A79" s="11">
         <v>800076</v>
       </c>
       <c r="D79" s="1" t="s">
@@ -5459,8 +4845,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:26">
-      <c r="A80" s="12">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A80" s="11">
         <v>800077</v>
       </c>
       <c r="D80" s="1" t="s">
@@ -5473,32 +4859,32 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="12">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A81" s="11">
         <v>800078</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="12">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A82" s="11">
         <v>800079</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="12">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A83" s="11">
         <v>800080</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="84" spans="1:26">
-      <c r="A84" s="12">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A84" s="11">
         <v>800081</v>
       </c>
       <c r="D84" s="1" t="s">
@@ -5514,7 +4900,7 @@
         <v>184</v>
       </c>
       <c r="J84" s="1">
-        <v>18.4</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="K84" s="1">
         <v>70</v>
@@ -5565,53 +4951,52 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="12">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A85" s="11">
         <v>800082</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="12">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A86" s="11">
         <v>800083</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="12">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A87" s="11">
         <v>800084</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="12">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="A88" s="11">
         <v>800085</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="11" t="s">
         <v>94</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C6:O14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="6" spans="3:12">
+    <row r="6" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C6" t="s">
         <v>95</v>
       </c>
@@ -5631,7 +5016,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="3:15">
+    <row r="7" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C7" t="s">
         <v>12</v>
       </c>
@@ -5654,7 +5039,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="3:15">
+    <row r="8" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C8" t="s">
         <v>4</v>
       </c>
@@ -5677,7 +5062,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="3:15">
+    <row r="9" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C9" t="s">
         <v>6</v>
       </c>
@@ -5700,7 +5085,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="3:15">
+    <row r="10" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C10" t="s">
         <v>14</v>
       </c>
@@ -5720,10 +5105,10 @@
         <v>110</v>
       </c>
       <c r="O10">
-        <v>0.033</v>
-      </c>
-    </row>
-    <row r="11" spans="3:15">
+        <v>3.3000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C11" t="s">
         <v>8</v>
       </c>
@@ -5746,7 +5131,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="3:15">
+    <row r="12" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C12" t="s">
         <v>10</v>
       </c>
@@ -5769,7 +5154,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="3:15">
+    <row r="13" spans="3:15" x14ac:dyDescent="0.15">
       <c r="C13" t="s">
         <v>116</v>
       </c>
@@ -5789,10 +5174,10 @@
         <v>110</v>
       </c>
       <c r="O13">
-        <v>0.033</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="3:12">
+        <v>3.3000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="3:15" ht="16.5" x14ac:dyDescent="0.15">
       <c r="C14" t="s">
         <v>117</v>
       </c>
@@ -5813,20 +5198,19 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
-  <headerFooter/>
 </worksheet>
 </file>